--- a/i18n/es.xlsx
+++ b/i18n/es.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -4167,144 +4167,9 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Birds Cards in Hand</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>No Goal</t>
-  </si>
-  <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
-  </si>
-  <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
-    <t>In Forest</t>
-  </si>
-  <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>Translated</t>
   </si>
   <si>
@@ -4372,6 +4237,141 @@
   </si>
   <si>
     <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
   </si>
 </sst>
 </file>
@@ -4381,7 +4381,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;PRAWDA&quot;;&quot;PRAWDA&quot;;&quot;FAŁSZ&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -4400,19 +4400,28 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4435,7 +4444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -4458,6 +4467,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4678,7 +4688,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1445</v>
+        <v>1400</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -5419,7 +5429,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1438</v>
+        <v>1393</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>134</v>
@@ -6982,7 +6992,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1439</v>
+        <v>1394</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>369</v>
@@ -7672,7 +7682,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>472</v>
@@ -8505,7 +8515,7 @@
         <v>606</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1442</v>
+        <v>1397</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>13</v>
@@ -10975,7 +10985,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="12" t="s">
-        <v>1444</v>
+        <v>1399</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>942</v>
@@ -11180,7 +11190,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>1440</v>
+        <v>1395</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>969</v>
@@ -12629,7 +12639,7 @@
         <v>1143</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>1443</v>
+        <v>1398</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>1062</v>
@@ -14397,7 +14407,7 @@
         <v>2000</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1377</v>
+        <v>1401</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>13</v>
@@ -14411,7 +14421,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1378</v>
+        <v>1402</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>13</v>
@@ -14425,7 +14435,7 @@
         <v>2002</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1379</v>
+        <v>1403</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>13</v>
@@ -14439,7 +14449,7 @@
         <v>2013</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1380</v>
+        <v>1404</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>13</v>
@@ -14453,7 +14463,7 @@
         <v>2014</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1381</v>
+        <v>1405</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>13</v>
@@ -14467,7 +14477,7 @@
         <v>2017</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1382</v>
+        <v>1406</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>13</v>
@@ -14481,7 +14491,7 @@
         <v>2010</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1383</v>
+        <v>1407</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>13</v>
@@ -14495,7 +14505,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1384</v>
+        <v>1408</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>13</v>
@@ -14509,7 +14519,7 @@
         <v>2021</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1385</v>
+        <v>1409</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>13</v>
@@ -14523,7 +14533,7 @@
         <v>2022</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1386</v>
+        <v>1410</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>13</v>
@@ -14537,7 +14547,7 @@
         <v>2012</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1387</v>
+        <v>1411</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>13</v>
@@ -14551,7 +14561,7 @@
         <v>2011</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1388</v>
+        <v>1412</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>13</v>
@@ -14565,7 +14575,7 @@
         <v>2015</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1389</v>
+        <v>1413</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>13</v>
@@ -14579,7 +14589,7 @@
         <v>2016</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1390</v>
+        <v>1414</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>13</v>
@@ -14593,7 +14603,7 @@
         <v>2023</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1391</v>
+        <v>1415</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>13</v>
@@ -14607,7 +14617,7 @@
         <v>2024</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1392</v>
+        <v>1416</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>13</v>
@@ -14621,7 +14631,7 @@
         <v>2020</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1393</v>
+        <v>1417</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>78</v>
@@ -14635,7 +14645,7 @@
         <v>2003</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1394</v>
+        <v>1377</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>78</v>
@@ -14649,7 +14659,7 @@
         <v>2004</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>78</v>
@@ -14663,7 +14673,7 @@
         <v>2006</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>1396</v>
+        <v>1419</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>78</v>
@@ -14677,7 +14687,7 @@
         <v>2005</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>1397</v>
+        <v>1420</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>78</v>
@@ -14691,7 +14701,7 @@
         <v>2018</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>1398</v>
+        <v>1421</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>78</v>
@@ -14705,7 +14715,7 @@
         <v>2009</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1399</v>
+        <v>1422</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>78</v>
@@ -14719,7 +14729,7 @@
         <v>2025</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1400</v>
+        <v>1423</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>78</v>
@@ -14733,7 +14743,7 @@
         <v>2007</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1401</v>
+        <v>1424</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>78</v>
@@ -14747,7 +14757,7 @@
         <v>2019</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>1402</v>
+        <v>1425</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>78</v>
@@ -14761,7 +14771,7 @@
         <v>2031</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>1403</v>
+        <v>1426</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>873</v>
@@ -14775,7 +14785,7 @@
         <v>2030</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1404</v>
+        <v>1427</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>873</v>
@@ -14789,7 +14799,7 @@
         <v>2033</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1405</v>
+        <v>1428</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>873</v>
@@ -14803,7 +14813,7 @@
         <v>2032</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1406</v>
+        <v>1429</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>873</v>
@@ -14817,7 +14827,7 @@
         <v>2026</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>1407</v>
+        <v>1430</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>873</v>
@@ -14831,7 +14841,7 @@
         <v>2027</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>1408</v>
+        <v>1431</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>873</v>
@@ -14845,7 +14855,7 @@
         <v>2029</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>1409</v>
+        <v>1432</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>873</v>
@@ -14859,7 +14869,7 @@
         <v>2028</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>1410</v>
+        <v>1433</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>873</v>
@@ -14872,8 +14882,8 @@
       <c r="A36" s="2">
         <v>2043</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>1411</v>
+      <c r="B36" s="14" t="s">
+        <v>1434</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>1062</v>
@@ -14887,7 +14897,7 @@
         <v>2040</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>1412</v>
+        <v>1435</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>1062</v>
@@ -14901,7 +14911,7 @@
         <v>2035</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>1413</v>
+        <v>1436</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>1062</v>
@@ -14915,7 +14925,7 @@
         <v>2041</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>1414</v>
+        <v>1437</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>1062</v>
@@ -14929,7 +14939,7 @@
         <v>2042</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>1415</v>
+        <v>1438</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>1062</v>
@@ -14943,7 +14953,7 @@
         <v>2044</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>1416</v>
+        <v>1439</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>1062</v>
@@ -14957,7 +14967,7 @@
         <v>2036</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>1417</v>
+        <v>1440</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>1062</v>
@@ -14971,7 +14981,7 @@
         <v>2034</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>1418</v>
+        <v>1441</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>1062</v>
@@ -14985,7 +14995,7 @@
         <v>2037</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1419</v>
+        <v>1442</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>1062</v>
@@ -14999,7 +15009,7 @@
         <v>2038</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>1420</v>
+        <v>1443</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>1062</v>
@@ -15013,7 +15023,7 @@
         <v>2039</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>1421</v>
+        <v>1444</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>1062</v>
@@ -15027,7 +15037,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>1422</v>
+        <v>1445</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>1062</v>
@@ -15061,55 +15071,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1423</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1424</v>
+        <v>1379</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1425</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1426</v>
+        <v>1381</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1427</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1429</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1430</v>
+        <v>1385</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1432</v>
+        <v>1387</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1434</v>
+        <v>1389</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1435</v>
+        <v>1390</v>
       </c>
     </row>
   </sheetData>
@@ -15135,12 +15145,12 @@
         <v>1240</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1437</v>
+        <v>1392</v>
       </c>
       <c r="B2" s="10" t="b">
         <f>TRUE()</f>
